--- a/WorkBot/main/data/orders/Hill & Markes/Hill & Markes_Triphammer_20260529.xlsx
+++ b/WorkBot/main/data/orders/Hill & Markes/Hill & Markes_Triphammer_20260529.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,6 +752,111 @@
         <v>53.54</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6G063015</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bag Poly - 6x3x15 LW</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E19" t="n">
+        <v>54.56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P4040XC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bag Sheet Pan Cover 30x43</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="E20" t="n">
+        <v>22.04</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PRI80134X60</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Masking Tape</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="E21" t="n">
+        <v>63.64</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TS12</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 12oz Square</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="E22" t="n">
+        <v>153.56</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WES183</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Wrap - Film (18")</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
